--- a/output/文中傳票維護匯入_全部合併_玉山銀行沖銷_202610.xlsx
+++ b/output/文中傳票維護匯入_全部合併_玉山銀行沖銷_202610.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP141"/>
+  <dimension ref="A1:AP170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_月宮_09/17~09/23外送款</t>
+          <t>門市營業現金存入銀行_月宮_2026-10-21~2026-10-25 多日累計</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2735,14 +2735,14 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>26451</v>
+        <v>25361</v>
       </c>
       <c r="O23" t="n">
-        <v>26451</v>
+        <v>25361</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款 (款項日: 09/17~09/23外送款)</t>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-21~2026-10-25 多日累計)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_月宮_09/17~09/23外送款</t>
+          <t>門市營業現金存入銀行_月宮_2026-10-21~2026-10-25 多日累計</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1130-03</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2827,14 +2827,14 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>26451</v>
+        <v>845</v>
       </c>
       <c r="O24" t="n">
-        <v>26451</v>
+        <v>845</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
+          <t>門市營業現金溢收調節 (差額 $845)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
@@ -2875,23 +2875,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/29營業款</t>
+          <t>門市營業現金存入銀行_月宮_2026-10-21~2026-10-25 多日累計</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-01</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2919,14 +2919,14 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>5408</v>
+        <v>24516</v>
       </c>
       <c r="O25" t="n">
-        <v>5408</v>
+        <v>24516</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約09/29營業款)</t>
+          <t>沖銷 2026-10-21~2026-10-25 多日累計 營業現金應收 (玉山 2026-10-27 存入)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -2972,18 +2972,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/29營業款</t>
+          <t>Uber Eats 外送撥款入帳_月宮_09/17~09/23外送款</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3011,14 +3011,14 @@
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>168</v>
+        <v>26451</v>
       </c>
       <c r="O26" t="n">
-        <v>168</v>
+        <v>26451</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>Uber Eats 外送撥款 (款項日: 09/17~09/23外送款)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -3064,18 +3064,18 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/29營業款</t>
+          <t>Uber Eats 外送撥款入帳_月宮_09/17~09/23外送款</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-03</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3103,14 +3103,14 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>26451</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>26451</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -3160,14 +3160,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3195,14 +3195,14 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>5584</v>
+        <v>5408</v>
       </c>
       <c r="O28" t="n">
-        <v>5584</v>
+        <v>5408</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>沖銷 約09/29營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約09/29營業款)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -3248,18 +3248,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約09/30電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/29營業款</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3287,14 +3287,14 @@
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>5261</v>
+        <v>168</v>
       </c>
       <c r="O29" t="n">
-        <v>5261</v>
+        <v>168</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約09/30電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -3340,18 +3340,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約09/30電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/29營業款</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3379,14 +3379,14 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>5261</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>5261</v>
+        <v>8</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>沖銷 約09/30電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
@@ -3427,23 +3427,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/30營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/29營業款</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3471,14 +3471,14 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>3578</v>
+        <v>5584</v>
       </c>
       <c r="O31" t="n">
-        <v>3578</v>
+        <v>5584</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約09/30營業款)</t>
+          <t>沖銷 約09/29營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -3519,23 +3519,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/30營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約09/30電支款</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3563,14 +3563,14 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>110</v>
+        <v>5261</v>
       </c>
       <c r="O32" t="n">
-        <v>110</v>
+        <v>5261</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約09/30電支款)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -3611,23 +3611,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/30營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約09/30電支款</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3655,14 +3655,14 @@
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>5261</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>5261</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約09/30電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -3712,14 +3712,14 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3747,14 +3747,14 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>3694</v>
+        <v>3578</v>
       </c>
       <c r="O34" t="n">
-        <v>3694</v>
+        <v>3578</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>沖銷 約09/30營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約09/30營業款)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
@@ -3800,18 +3800,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/01電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/30營業款</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3839,14 +3839,14 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>6237</v>
+        <v>110</v>
       </c>
       <c r="O35" t="n">
-        <v>6237</v>
+        <v>110</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/01電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
@@ -3892,18 +3892,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/01電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/30營業款</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3931,14 +3931,14 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>6237</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>6237</v>
+        <v>6</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>沖銷 約10/01電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
@@ -3979,23 +3979,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/01營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約09/30營業款</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4023,14 +4023,14 @@
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>4753</v>
+        <v>3694</v>
       </c>
       <c r="O37" t="n">
-        <v>4753</v>
+        <v>3694</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/01營業款)</t>
+          <t>沖銷 約09/30營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -4071,23 +4071,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/01營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/01電支款</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4115,14 +4115,14 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>148</v>
+        <v>6237</v>
       </c>
       <c r="O38" t="n">
-        <v>148</v>
+        <v>6237</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/01電支款)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
@@ -4163,23 +4163,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/01營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/01電支款</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4207,14 +4207,14 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>6237</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>6237</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/01電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -4264,14 +4264,14 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4299,14 +4299,14 @@
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>4908</v>
+        <v>4753</v>
       </c>
       <c r="O40" t="n">
-        <v>4908</v>
+        <v>4753</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>沖銷 約10/01營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/01營業款)</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -4352,18 +4352,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/04電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/01營業款</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4391,14 +4391,14 @@
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>6360</v>
+        <v>148</v>
       </c>
       <c r="O41" t="n">
-        <v>6360</v>
+        <v>148</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/04電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -4444,18 +4444,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/04電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/01營業款</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4483,14 +4483,14 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>6360</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
-        <v>6360</v>
+        <v>7</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>沖銷 約10/04電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -4531,23 +4531,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/03營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/01營業款</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4575,14 +4575,14 @@
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>16993</v>
+        <v>4908</v>
       </c>
       <c r="O43" t="n">
-        <v>16993</v>
+        <v>4908</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/03營業款)</t>
+          <t>沖銷 約10/01營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -4623,23 +4623,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/03營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/04電支款</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4667,14 +4667,14 @@
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>527</v>
+        <v>6360</v>
       </c>
       <c r="O44" t="n">
-        <v>527</v>
+        <v>6360</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/04電支款)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr"/>
@@ -4715,23 +4715,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/03營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/04電支款</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4759,14 +4759,14 @@
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>26</v>
+        <v>6360</v>
       </c>
       <c r="O45" t="n">
-        <v>26</v>
+        <v>6360</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/04電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr"/>
@@ -4816,14 +4816,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4851,14 +4851,14 @@
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>17546</v>
+        <v>16993</v>
       </c>
       <c r="O46" t="n">
-        <v>17546</v>
+        <v>16993</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>沖銷 約10/03營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/03營業款)</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr"/>
@@ -4904,18 +4904,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/05電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/03營業款</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4943,14 +4943,14 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>30840</v>
+        <v>527</v>
       </c>
       <c r="O47" t="n">
-        <v>30840</v>
+        <v>527</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/05電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
@@ -4996,18 +4996,18 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/05電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/03營業款</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5035,14 +5035,14 @@
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>30840</v>
+        <v>26</v>
       </c>
       <c r="O48" t="n">
-        <v>30840</v>
+        <v>26</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
@@ -5083,23 +5083,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/05營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/03營業款</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5127,14 +5127,14 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>2668</v>
+        <v>17546</v>
       </c>
       <c r="O49" t="n">
-        <v>2668</v>
+        <v>17546</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/05營業款)</t>
+          <t>沖銷 約10/03營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr"/>
@@ -5175,23 +5175,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/05營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/05電支款</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5219,14 +5219,14 @@
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>83</v>
+        <v>30840</v>
       </c>
       <c r="O50" t="n">
-        <v>83</v>
+        <v>30840</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/05電支款)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
@@ -5267,23 +5267,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/05營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/05電支款</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>30840</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>30840</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr"/>
@@ -5368,14 +5368,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5403,14 +5403,14 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>2755</v>
+        <v>2668</v>
       </c>
       <c r="O52" t="n">
-        <v>2755</v>
+        <v>2668</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>沖銷 約10/05營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/05營業款)</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr"/>
@@ -5456,18 +5456,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/06電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/05營業款</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5495,14 +5495,14 @@
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>6518</v>
+        <v>83</v>
       </c>
       <c r="O53" t="n">
-        <v>6518</v>
+        <v>83</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/06電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr"/>
@@ -5548,18 +5548,18 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/06電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/05營業款</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5587,14 +5587,14 @@
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>6518</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>6518</v>
+        <v>4</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>沖銷 約10/06電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr"/>
@@ -5635,23 +5635,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/07電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/05營業款</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5679,14 +5679,14 @@
         <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>6908</v>
+        <v>2755</v>
       </c>
       <c r="O55" t="n">
-        <v>6908</v>
+        <v>2755</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/07電支款)</t>
+          <t>沖銷 約10/05營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr"/>
@@ -5727,23 +5727,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/07電支款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/06電支款</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5771,14 +5771,14 @@
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>6908</v>
+        <v>6518</v>
       </c>
       <c r="O56" t="n">
-        <v>6908</v>
+        <v>6518</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>沖銷 約10/07電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/06電支款)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr"/>
@@ -5819,23 +5819,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/06營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/06電支款</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5863,14 +5863,14 @@
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>3075</v>
+        <v>6518</v>
       </c>
       <c r="O57" t="n">
-        <v>3075</v>
+        <v>6518</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/06營業款)</t>
+          <t>沖銷 約10/06電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr"/>
@@ -5916,18 +5916,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/06營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/07電支款</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5955,14 +5955,14 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>95</v>
+        <v>6908</v>
       </c>
       <c r="O58" t="n">
-        <v>95</v>
+        <v>6908</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/07電支款)</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
@@ -6008,18 +6008,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/06營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/07電支款</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6047,14 +6047,14 @@
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>6908</v>
       </c>
       <c r="O59" t="n">
-        <v>5</v>
+        <v>6908</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/07電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr"/>
@@ -6104,14 +6104,14 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6139,14 +6139,14 @@
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>3175</v>
+        <v>3075</v>
       </c>
       <c r="O60" t="n">
-        <v>3175</v>
+        <v>3075</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>沖銷 約10/06營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/06營業款)</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr"/>
@@ -6187,23 +6187,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/11電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/06營業款</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6231,14 +6231,14 @@
         <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>7157</v>
+        <v>95</v>
       </c>
       <c r="O61" t="n">
-        <v>7157</v>
+        <v>95</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/11電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr"/>
@@ -6279,23 +6279,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/11電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/06營業款</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6323,14 +6323,14 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>7157</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
-        <v>7157</v>
+        <v>5</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>沖銷 約10/11電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr"/>
@@ -6371,23 +6371,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/08營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/06營業款</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6415,14 +6415,14 @@
         <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>3005</v>
+        <v>3175</v>
       </c>
       <c r="O63" t="n">
-        <v>3005</v>
+        <v>3175</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/08營業款)</t>
+          <t>沖銷 約10/06營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr"/>
@@ -6468,18 +6468,18 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/08營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/11電支款</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6507,14 +6507,14 @@
         <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>93</v>
+        <v>7157</v>
       </c>
       <c r="O64" t="n">
-        <v>93</v>
+        <v>7157</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/11電支款)</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr"/>
@@ -6560,18 +6560,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/08營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/11電支款</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6599,14 +6599,14 @@
         <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>7157</v>
       </c>
       <c r="O65" t="n">
-        <v>5</v>
+        <v>7157</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/11電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
@@ -6656,14 +6656,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6691,14 +6691,14 @@
         <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>3103</v>
+        <v>3005</v>
       </c>
       <c r="O66" t="n">
-        <v>3103</v>
+        <v>3005</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>沖銷 約10/08營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/08營業款)</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr"/>
@@ -6744,18 +6744,18 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>偷訂餐飲科技撥款入帳_月宮</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/08營業款</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6783,14 +6783,14 @@
         <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>1870</v>
+        <v>93</v>
       </c>
       <c r="O67" t="n">
-        <v>1870</v>
+        <v>93</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>偷訂平台撥款入帳</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr"/>
@@ -6836,18 +6836,18 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>偷訂餐飲科技撥款入帳_月宮</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/08營業款</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1130-05</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6875,14 +6875,14 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>1870</v>
+        <v>5</v>
       </c>
       <c r="O68" t="n">
-        <v>1870</v>
+        <v>5</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>沖銷 偷訂 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr"/>
@@ -6923,23 +6923,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/10營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/08營業款</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6967,14 +6967,14 @@
         <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>18335</v>
+        <v>3103</v>
       </c>
       <c r="O69" t="n">
-        <v>18335</v>
+        <v>3103</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/10營業款)</t>
+          <t>沖銷 約10/08營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr"/>
@@ -7015,23 +7015,23 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/10營業款</t>
+          <t>偷訂餐飲科技撥款入帳_月宮</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7059,14 +7059,14 @@
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>568</v>
+        <v>1870</v>
       </c>
       <c r="O70" t="n">
-        <v>568</v>
+        <v>1870</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>偷訂平台撥款入帳</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr"/>
@@ -7107,23 +7107,23 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/10營業款</t>
+          <t>偷訂餐飲科技撥款入帳_月宮</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-05</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7151,14 +7151,14 @@
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>28</v>
+        <v>1870</v>
       </c>
       <c r="O71" t="n">
-        <v>28</v>
+        <v>1870</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 偷訂 應收帳款</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr"/>
@@ -7208,14 +7208,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7243,14 +7243,14 @@
         <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>18931</v>
+        <v>18335</v>
       </c>
       <c r="O72" t="n">
-        <v>18931</v>
+        <v>18335</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>沖銷 約10/10營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/10營業款)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr"/>
@@ -7296,18 +7296,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/12電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/10營業款</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7335,14 +7335,14 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>32962</v>
+        <v>568</v>
       </c>
       <c r="O73" t="n">
-        <v>32962</v>
+        <v>568</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/12電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr"/>
@@ -7388,18 +7388,18 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/12電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/10營業款</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7427,14 +7427,14 @@
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>32962</v>
+        <v>28</v>
       </c>
       <c r="O74" t="n">
-        <v>32962</v>
+        <v>28</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr"/>
@@ -7475,23 +7475,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/13電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/10營業款</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7519,14 +7519,14 @@
         <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>5780</v>
+        <v>18931</v>
       </c>
       <c r="O75" t="n">
-        <v>5780</v>
+        <v>18931</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/13電支款)</t>
+          <t>沖銷 約10/10營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr"/>
@@ -7567,23 +7567,23 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/13電支款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/12電支款</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7611,14 +7611,14 @@
         <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>5780</v>
+        <v>32962</v>
       </c>
       <c r="O76" t="n">
-        <v>5780</v>
+        <v>32962</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>沖銷 約10/13電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/12電支款)</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr"/>
@@ -7659,23 +7659,23 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/12營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/12電支款</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7703,14 +7703,14 @@
         <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>2926</v>
+        <v>32962</v>
       </c>
       <c r="O77" t="n">
-        <v>2926</v>
+        <v>32962</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/12營業款)</t>
+          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr"/>
@@ -7756,18 +7756,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/12營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/13電支款</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7795,14 +7795,14 @@
         <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>90</v>
+        <v>5780</v>
       </c>
       <c r="O78" t="n">
-        <v>90</v>
+        <v>5780</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/13電支款)</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr"/>
@@ -7848,18 +7848,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/12營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/13電支款</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7887,14 +7887,14 @@
         <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>5780</v>
       </c>
       <c r="O79" t="n">
-        <v>5</v>
+        <v>5780</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/13電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr"/>
@@ -7944,14 +7944,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7979,14 +7979,14 @@
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>3021</v>
+        <v>2926</v>
       </c>
       <c r="O80" t="n">
-        <v>3021</v>
+        <v>2926</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>沖銷 約10/12營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/12營業款)</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr"/>
@@ -8027,23 +8027,23 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_月宮_10/01~10/07外送款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/12營業款</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8071,14 +8071,14 @@
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>28996</v>
+        <v>90</v>
       </c>
       <c r="O81" t="n">
-        <v>28996</v>
+        <v>90</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款 (款項日: 10/01~10/07外送款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr"/>
@@ -8119,23 +8119,23 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_月宮_10/01~10/07外送款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/12營業款</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1130-03</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8163,14 +8163,14 @@
         <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>28996</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>28996</v>
+        <v>5</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr"/>
@@ -8211,23 +8211,23 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/14電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/12營業款</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8255,14 +8255,14 @@
         <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>7272</v>
+        <v>3021</v>
       </c>
       <c r="O83" t="n">
-        <v>7272</v>
+        <v>3021</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/14電支款)</t>
+          <t>沖銷 約10/12營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr"/>
@@ -8308,18 +8308,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/14電支款</t>
+          <t>Uber Eats 外送撥款入帳_月宮_10/01~10/07外送款</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8347,14 +8347,14 @@
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>7272</v>
+        <v>28996</v>
       </c>
       <c r="O84" t="n">
-        <v>7272</v>
+        <v>28996</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>沖銷 約10/14電支款 LINE Pay 應收帳款</t>
+          <t>Uber Eats 外送撥款 (款項日: 10/01~10/07外送款)</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr"/>
@@ -8400,18 +8400,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/13營業款</t>
+          <t>Uber Eats 外送撥款入帳_月宮_10/01~10/07外送款</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-03</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8439,14 +8439,14 @@
         <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>2269</v>
+        <v>28996</v>
       </c>
       <c r="O85" t="n">
-        <v>2269</v>
+        <v>28996</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/13營業款)</t>
+          <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr"/>
@@ -8492,18 +8492,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/13營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/14電支款</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8531,14 +8531,14 @@
         <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>70</v>
+        <v>7272</v>
       </c>
       <c r="O86" t="n">
-        <v>70</v>
+        <v>7272</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/14電支款)</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr"/>
@@ -8584,18 +8584,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/13營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/14電支款</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8623,14 +8623,14 @@
         <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>7272</v>
       </c>
       <c r="O87" t="n">
-        <v>4</v>
+        <v>7272</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/14電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr"/>
@@ -8680,14 +8680,14 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8715,14 +8715,14 @@
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>2343</v>
+        <v>2269</v>
       </c>
       <c r="O88" t="n">
-        <v>2343</v>
+        <v>2269</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>沖銷 約10/13營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/13營業款)</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr"/>
@@ -8763,23 +8763,23 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/15電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/13營業款</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8807,14 +8807,14 @@
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>7226</v>
+        <v>70</v>
       </c>
       <c r="O89" t="n">
-        <v>7226</v>
+        <v>70</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/15電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr"/>
@@ -8855,23 +8855,23 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/15電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/13營業款</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8899,14 +8899,14 @@
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>7226</v>
+        <v>4</v>
       </c>
       <c r="O90" t="n">
-        <v>7226</v>
+        <v>4</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>沖銷 約10/15電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr"/>
@@ -8947,23 +8947,23 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/14營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/13營業款</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8991,14 +8991,14 @@
         <v>1</v>
       </c>
       <c r="N91" t="n">
-        <v>4262</v>
+        <v>2343</v>
       </c>
       <c r="O91" t="n">
-        <v>4262</v>
+        <v>2343</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/14營業款)</t>
+          <t>沖銷 約10/13營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr"/>
@@ -9044,18 +9044,18 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/14營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/15電支款</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9083,14 +9083,14 @@
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>132</v>
+        <v>7226</v>
       </c>
       <c r="O92" t="n">
-        <v>132</v>
+        <v>7226</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/15電支款)</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr"/>
@@ -9136,18 +9136,18 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/14營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/15電支款</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9175,14 +9175,14 @@
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>7</v>
+        <v>7226</v>
       </c>
       <c r="O93" t="n">
-        <v>7</v>
+        <v>7226</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/15電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr"/>
@@ -9232,14 +9232,14 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9267,14 +9267,14 @@
         <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>4401</v>
+        <v>4262</v>
       </c>
       <c r="O94" t="n">
-        <v>4401</v>
+        <v>4262</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>沖銷 約10/14營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/14營業款)</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr"/>
@@ -9315,23 +9315,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/15營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/14營業款</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9359,14 +9359,14 @@
         <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>2759</v>
+        <v>132</v>
       </c>
       <c r="O95" t="n">
-        <v>2759</v>
+        <v>132</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/15營業款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr"/>
@@ -9407,23 +9407,23 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/15營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/14營業款</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9451,14 +9451,14 @@
         <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="O96" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr"/>
@@ -9499,23 +9499,23 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/15營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/14營業款</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9543,14 +9543,14 @@
         <v>1</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>4401</v>
       </c>
       <c r="O97" t="n">
-        <v>4</v>
+        <v>4401</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/14營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr"/>
@@ -9600,14 +9600,14 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9635,14 +9635,14 @@
         <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>2849</v>
+        <v>2759</v>
       </c>
       <c r="O98" t="n">
-        <v>2849</v>
+        <v>2759</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>沖銷 約10/15營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/15營業款)</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr"/>
@@ -9688,18 +9688,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/18電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/15營業款</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9727,14 +9727,14 @@
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>7337</v>
+        <v>86</v>
       </c>
       <c r="O99" t="n">
-        <v>7337</v>
+        <v>86</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/18電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr"/>
@@ -9780,18 +9780,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/18電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/15營業款</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9819,14 +9819,14 @@
         <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>7337</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
-        <v>7337</v>
+        <v>4</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>沖銷 約10/18電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr"/>
@@ -9867,23 +9867,23 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/17營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/15營業款</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9911,14 +9911,14 @@
         <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>8844</v>
+        <v>2849</v>
       </c>
       <c r="O101" t="n">
-        <v>8844</v>
+        <v>2849</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/17營業款)</t>
+          <t>沖銷 約10/15營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr"/>
@@ -9959,23 +9959,23 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/17營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/18電支款</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10003,14 +10003,14 @@
         <v>1</v>
       </c>
       <c r="N102" t="n">
-        <v>274</v>
+        <v>7337</v>
       </c>
       <c r="O102" t="n">
-        <v>274</v>
+        <v>7337</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/18電支款)</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr"/>
@@ -10051,23 +10051,23 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/17營業款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/18電支款</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10095,14 +10095,14 @@
         <v>1</v>
       </c>
       <c r="N103" t="n">
-        <v>14</v>
+        <v>7337</v>
       </c>
       <c r="O103" t="n">
-        <v>14</v>
+        <v>7337</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>沖銷 約10/18電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr"/>
@@ -10152,14 +10152,14 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10187,14 +10187,14 @@
         <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>9132</v>
+        <v>8844</v>
       </c>
       <c r="O104" t="n">
-        <v>9132</v>
+        <v>8844</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>沖銷 約10/17營業款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/17營業款)</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr"/>
@@ -10240,18 +10240,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/19電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/17營業款</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10279,14 +10279,14 @@
         <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>31812</v>
+        <v>274</v>
       </c>
       <c r="O105" t="n">
-        <v>31812</v>
+        <v>274</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/19電支款)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr"/>
@@ -10332,18 +10332,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/19電支款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/17營業款</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10371,14 +10371,14 @@
         <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>31812</v>
+        <v>14</v>
       </c>
       <c r="O106" t="n">
-        <v>31812</v>
+        <v>14</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>沖銷 約10/19電支款 LINE Pay 應收帳款</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr"/>
@@ -10419,28 +10419,28 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-09-30 (上月跨月款)</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/17營業款</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10463,14 +10463,14 @@
         <v>1</v>
       </c>
       <c r="N107" t="n">
-        <v>11340</v>
+        <v>9132</v>
       </c>
       <c r="O107" t="n">
-        <v>11340</v>
+        <v>9132</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-09-30 (上月跨月款))</t>
+          <t>沖銷 約10/17營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr"/>
@@ -10511,28 +10511,28 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-09-30 (上月跨月款)</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/19電支款</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -10555,14 +10555,14 @@
         <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>11340</v>
+        <v>31812</v>
       </c>
       <c r="O108" t="n">
-        <v>11340</v>
+        <v>31812</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>沖銷 2026-09-30 (上月跨月款) 營業現金應收 (玉山 2026-10-01 存入)</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/19電支款)</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
@@ -10603,28 +10603,28 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-01</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/19電支款</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -10647,14 +10647,14 @@
         <v>1</v>
       </c>
       <c r="N109" t="n">
-        <v>9880</v>
+        <v>31812</v>
       </c>
       <c r="O109" t="n">
-        <v>9880</v>
+        <v>31812</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-01)</t>
+          <t>沖銷 約10/19電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr"/>
@@ -10695,28 +10695,28 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-01</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/20電支款</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -10739,14 +10739,14 @@
         <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>9880</v>
+        <v>4085</v>
       </c>
       <c r="O110" t="n">
-        <v>9880</v>
+        <v>4085</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-01 營業現金應收 (玉山 2026-10-02 存入)</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/20電支款)</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr"/>
@@ -10787,28 +10787,28 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-02~2026-10-04 多日累計</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/20電支款</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -10831,14 +10831,14 @@
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>57305</v>
+        <v>4085</v>
       </c>
       <c r="O111" t="n">
-        <v>57305</v>
+        <v>4085</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-02~2026-10-04 多日累計)</t>
+          <t>沖銷 約10/20電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr"/>
@@ -10879,28 +10879,28 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-02~2026-10-04 多日累計</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/19營業款</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -10923,14 +10923,14 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>2993</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>2993</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>門市營業現金溢收調節 (差額 $5)</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/19營業款)</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr"/>
@@ -10971,28 +10971,28 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-02~2026-10-04 多日累計</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/19營業款</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11015,14 +11015,14 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>57300</v>
+        <v>92</v>
       </c>
       <c r="O113" t="n">
-        <v>57300</v>
+        <v>92</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-02~2026-10-04 多日累計 營業現金應收 (玉山 2026-10-05 存入)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr"/>
@@ -11063,28 +11063,28 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-05</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/19營業款</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11107,14 +11107,14 @@
         <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>9520</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
-        <v>9520</v>
+        <v>5</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-05)</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr"/>
@@ -11155,28 +11155,28 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-05</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/19營業款</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
         <v>2</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11199,14 +11199,14 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>9520</v>
+        <v>3090</v>
       </c>
       <c r="O115" t="n">
-        <v>9520</v>
+        <v>3090</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-05 營業現金應收 (玉山 2026-10-06 存入)</t>
+          <t>沖銷 約10/19營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr"/>
@@ -11247,12 +11247,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-06~2026-10-07 多日累計</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/21電支款</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11291,14 +11291,14 @@
         <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>27570</v>
+        <v>8202</v>
       </c>
       <c r="O116" t="n">
-        <v>27570</v>
+        <v>8202</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-06~2026-10-07 多日累計)</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/21電支款)</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr"/>
@@ -11339,12 +11339,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-06~2026-10-07 多日累計</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/21電支款</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11383,14 +11383,14 @@
         <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>27570</v>
+        <v>8202</v>
       </c>
       <c r="O117" t="n">
-        <v>27570</v>
+        <v>8202</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-06~2026-10-07 多日累計 營業現金應收 (玉山 2026-10-08 存入)</t>
+          <t>沖銷 約10/21電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr"/>
@@ -11431,12 +11431,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-08~2026-10-11 多日累計</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/20營業款</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11475,14 +11475,14 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>73748</v>
+        <v>2614</v>
       </c>
       <c r="O118" t="n">
-        <v>73748</v>
+        <v>2614</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-08~2026-10-11 多日累計)</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/20營業款)</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr"/>
@@ -11523,28 +11523,28 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-08~2026-10-11 多日累計</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/20營業款</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>2</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -11567,14 +11567,14 @@
         <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>73748</v>
+        <v>81</v>
       </c>
       <c r="O119" t="n">
-        <v>73748</v>
+        <v>81</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-08~2026-10-11 多日累計 營業現金應收 (玉山 2026-10-12 存入)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr"/>
@@ -11615,28 +11615,28 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-12</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/20營業款</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -11659,14 +11659,14 @@
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>12400</v>
+        <v>4</v>
       </c>
       <c r="O120" t="n">
-        <v>12400</v>
+        <v>4</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-12)</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr"/>
@@ -11707,28 +11707,28 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-12</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/20營業款</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121" t="n">
         <v>2</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -11751,14 +11751,14 @@
         <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>12400</v>
+        <v>2699</v>
       </c>
       <c r="O121" t="n">
-        <v>12400</v>
+        <v>2699</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-12 營業現金應收 (玉山 2026-10-13 存入)</t>
+          <t>沖銷 約10/20營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr"/>
@@ -11799,12 +11799,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-13</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -11843,14 +11843,14 @@
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>18810</v>
+        <v>3994</v>
       </c>
       <c r="O122" t="n">
-        <v>18810</v>
+        <v>3994</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-13)</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/24營業款)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr"/>
@@ -11891,28 +11891,28 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>門市營業現金存入銀行_隨意小吃_2026-10-13</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1130-01</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -11935,14 +11935,14 @@
         <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>18810</v>
+        <v>124</v>
       </c>
       <c r="O123" t="n">
-        <v>18810</v>
+        <v>124</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-13 營業現金應收 (玉山 2026-10-14 存入)</t>
+          <t>LINE Pay 交易手續費</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr"/>
@@ -11983,28 +11983,28 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_隨意小吃_09/17~09/23外送款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12027,14 +12027,14 @@
         <v>1</v>
       </c>
       <c r="N124" t="n">
-        <v>14615</v>
+        <v>6</v>
       </c>
       <c r="O124" t="n">
-        <v>14615</v>
+        <v>6</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款 (款項日: 09/17~09/23外送款)</t>
+          <t>LINE Pay 手續費進項稅額</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr"/>
@@ -12075,28 +12075,28 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_隨意小吃_09/17~09/23外送款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F125" t="n">
         <v>2</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1130-03</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12119,14 +12119,14 @@
         <v>1</v>
       </c>
       <c r="N125" t="n">
-        <v>14615</v>
+        <v>4124</v>
       </c>
       <c r="O125" t="n">
-        <v>14615</v>
+        <v>4124</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
+          <t>沖銷 約10/24營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr"/>
@@ -12167,12 +12167,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12211,14 +12211,14 @@
         <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>14009</v>
+        <v>1667</v>
       </c>
       <c r="O126" t="n">
-        <v>14009</v>
+        <v>1667</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/03營業款)</t>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/24營業款)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr"/>
@@ -12259,12 +12259,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12303,10 +12303,10 @@
         <v>1</v>
       </c>
       <c r="N127" t="n">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="O127" t="n">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12395,10 +12395,10 @@
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="O128" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+          <t>連加網路(LINE Pay)撥款入帳_月宮_約10/24營業款</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -12487,14 +12487,14 @@
         <v>1</v>
       </c>
       <c r="N129" t="n">
-        <v>14465</v>
+        <v>1721</v>
       </c>
       <c r="O129" t="n">
-        <v>14465</v>
+        <v>1721</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>沖銷 約10/03營業款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/24營業款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr"/>
@@ -12535,12 +12535,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/05電支款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/26電支款</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -12579,14 +12579,14 @@
         <v>1</v>
       </c>
       <c r="N130" t="n">
-        <v>29827</v>
+        <v>6789</v>
       </c>
       <c r="O130" t="n">
-        <v>29827</v>
+        <v>6789</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/05電支款)</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/26電支款)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr"/>
@@ -12627,12 +12627,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/05電支款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/26電支款</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -12671,14 +12671,14 @@
         <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>29827</v>
+        <v>6789</v>
       </c>
       <c r="O131" t="n">
-        <v>29827</v>
+        <v>6789</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/26電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr"/>
@@ -12719,12 +12719,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Foodpanda 外送撥款入帳_隨意小吃_上月下半月(16~30日)外送款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/26電支款</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -12763,14 +12763,14 @@
         <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>7255</v>
+        <v>4681</v>
       </c>
       <c r="O132" t="n">
-        <v>7255</v>
+        <v>4681</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Foodpanda 外送撥款 (款項日: 上月下半月(16~30日)外送款)</t>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/26電支款)</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr"/>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Foodpanda 外送撥款入帳_隨意小吃_上月下半月(16~30日)外送款</t>
+          <t>連加電子支付(LINE Pay)提領入帳_月宮_約10/26電支款</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1130-04</t>
+          <t>1130-02</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -12855,14 +12855,14 @@
         <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>7255</v>
+        <v>4681</v>
       </c>
       <c r="O133" t="n">
-        <v>7255</v>
+        <v>4681</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>沖銷 上月下半月(16~30日)外送款 Foodpanda 應收帳款</t>
+          <t>沖銷 約10/26電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr"/>
@@ -12903,12 +12903,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+          <t>偷訂餐飲科技撥款入帳_月宮</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -12947,14 +12947,14 @@
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>18024</v>
+        <v>1343</v>
       </c>
       <c r="O134" t="n">
-        <v>18024</v>
+        <v>1343</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/10營業款)</t>
+          <t>偷訂平台撥款入帳</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr"/>
@@ -12995,28 +12995,28 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+          <t>偷訂餐飲科技撥款入帳_月宮</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1130-05</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13039,14 +13039,14 @@
         <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>558</v>
+        <v>1343</v>
       </c>
       <c r="O135" t="n">
-        <v>558</v>
+        <v>1343</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>LINE Pay 交易手續費</t>
+          <t>沖銷 偷訂 應收帳款</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr"/>
@@ -13087,23 +13087,23 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+          <t>門市營業現金存入銀行_隨意小吃_2026-09-30 (上月跨月款)</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -13131,14 +13131,14 @@
         <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>28</v>
+        <v>11340</v>
       </c>
       <c r="O136" t="n">
-        <v>28</v>
+        <v>11340</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>LINE Pay 手續費進項稅額</t>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-09-30 (上月跨月款))</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr"/>
@@ -13179,23 +13179,23 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+          <t>門市營業現金存入銀行_隨意小吃_2026-09-30 (上月跨月款)</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
         <v>2</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1130-01</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -13223,14 +13223,14 @@
         <v>1</v>
       </c>
       <c r="N137" t="n">
-        <v>18610</v>
+        <v>11340</v>
       </c>
       <c r="O137" t="n">
-        <v>18610</v>
+        <v>11340</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>沖銷 約10/10營業款 LINE Pay 應收帳款</t>
+          <t>沖銷 2026-09-30 (上月跨月款) 營業現金應收 (玉山 2026-10-01 存入)</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr"/>
@@ -13271,12 +13271,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/12電支款</t>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-01</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -13315,14 +13315,14 @@
         <v>1</v>
       </c>
       <c r="N138" t="n">
-        <v>32130</v>
+        <v>9880</v>
       </c>
       <c r="O138" t="n">
-        <v>32130</v>
+        <v>9880</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>LINE Pay 電子支付提領 (款項日: 約10/12電支款)</t>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-01)</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr"/>
@@ -13363,12 +13363,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/12電支款</t>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-01</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1130-02</t>
+          <t>1130-01</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13407,14 +13407,14 @@
         <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>32130</v>
+        <v>9880</v>
       </c>
       <c r="O139" t="n">
-        <v>32130</v>
+        <v>9880</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 2026-10-01 營業現金應收 (玉山 2026-10-02 存入)</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr"/>
@@ -13455,12 +13455,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_隨意小吃_10/01~10/07外送款</t>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-02~2026-10-04 多日累計</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -13499,14 +13499,14 @@
         <v>1</v>
       </c>
       <c r="N140" t="n">
-        <v>5301</v>
+        <v>57305</v>
       </c>
       <c r="O140" t="n">
-        <v>5301</v>
+        <v>57305</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款 (款項日: 10/01~10/07外送款)</t>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-02~2026-10-04 多日累計)</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr"/>
@@ -13547,12 +13547,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Uber Eats 外送撥款入帳_隨意小吃_10/01~10/07外送款</t>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-02~2026-10-04 多日累計</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1130-03</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13591,14 +13591,14 @@
         <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>5301</v>
+        <v>5</v>
       </c>
       <c r="O141" t="n">
-        <v>5301</v>
+        <v>5</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
+          <t>門市營業現金溢收調節 (差額 $5)</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr"/>
@@ -13628,6 +13628,2674 @@
       <c r="AO141" t="inlineStr"/>
       <c r="AP141" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-02~2026-10-04 多日累計</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>1130-01</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>57300</v>
+      </c>
+      <c r="O142" t="n">
+        <v>57300</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-02~2026-10-04 多日累計 營業現金應收 (玉山 2026-10-05 存入)</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr"/>
+      <c r="AJ142" t="inlineStr"/>
+      <c r="AK142" t="inlineStr"/>
+      <c r="AL142" t="inlineStr"/>
+      <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr"/>
+      <c r="AO142" t="inlineStr"/>
+      <c r="AP142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>3</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-05</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>9520</v>
+      </c>
+      <c r="O143" t="n">
+        <v>9520</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-05)</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="inlineStr"/>
+      <c r="AK143" t="inlineStr"/>
+      <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr"/>
+      <c r="AO143" t="inlineStr"/>
+      <c r="AP143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-05</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1130-01</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" t="n">
+        <v>9520</v>
+      </c>
+      <c r="O144" t="n">
+        <v>9520</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-05 營業現金應收 (玉山 2026-10-06 存入)</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr"/>
+      <c r="AJ144" t="inlineStr"/>
+      <c r="AK144" t="inlineStr"/>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr"/>
+      <c r="AO144" t="inlineStr"/>
+      <c r="AP144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-06~2026-10-07 多日累計</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>27570</v>
+      </c>
+      <c r="O145" t="n">
+        <v>27570</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-06~2026-10-07 多日累計)</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
+      <c r="AJ145" t="inlineStr"/>
+      <c r="AK145" t="inlineStr"/>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="inlineStr"/>
+      <c r="AP145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-06~2026-10-07 多日累計</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>2</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1130-01</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>27570</v>
+      </c>
+      <c r="O146" t="n">
+        <v>27570</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-06~2026-10-07 多日累計 營業現金應收 (玉山 2026-10-08 存入)</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="inlineStr"/>
+      <c r="AK146" t="inlineStr"/>
+      <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr"/>
+      <c r="AO146" t="inlineStr"/>
+      <c r="AP146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-08~2026-10-11 多日累計</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>73748</v>
+      </c>
+      <c r="O147" t="n">
+        <v>73748</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-08~2026-10-11 多日累計)</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="inlineStr"/>
+      <c r="AK147" t="inlineStr"/>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="inlineStr"/>
+      <c r="AP147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>3</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-08~2026-10-11 多日累計</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1130-01</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>73748</v>
+      </c>
+      <c r="O148" t="n">
+        <v>73748</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-08~2026-10-11 多日累計 營業現金應收 (玉山 2026-10-12 存入)</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
+      <c r="AJ148" t="inlineStr"/>
+      <c r="AK148" t="inlineStr"/>
+      <c r="AL148" t="inlineStr"/>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr"/>
+      <c r="AO148" t="inlineStr"/>
+      <c r="AP148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>3</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-12</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>12400</v>
+      </c>
+      <c r="O149" t="n">
+        <v>12400</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-12)</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr"/>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr"/>
+      <c r="AJ149" t="inlineStr"/>
+      <c r="AK149" t="inlineStr"/>
+      <c r="AL149" t="inlineStr"/>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr"/>
+      <c r="AO149" t="inlineStr"/>
+      <c r="AP149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>3</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-12</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>1130-01</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>12400</v>
+      </c>
+      <c r="O150" t="n">
+        <v>12400</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-12 營業現金應收 (玉山 2026-10-13 存入)</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr"/>
+      <c r="AJ150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr"/>
+      <c r="AO150" t="inlineStr"/>
+      <c r="AP150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>3</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-13</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>18810</v>
+      </c>
+      <c r="O151" t="n">
+        <v>18810</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>營業現金存入玉山銀行 (所屬款項日: 2026-10-13)</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr"/>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="inlineStr"/>
+      <c r="AP151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>門市營業現金存入銀行_隨意小吃_2026-10-13</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1130-01</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>18810</v>
+      </c>
+      <c r="O152" t="n">
+        <v>18810</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-13 營業現金應收 (玉山 2026-10-14 存入)</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr"/>
+      <c r="AL152" t="inlineStr"/>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr"/>
+      <c r="AO152" t="inlineStr"/>
+      <c r="AP152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Uber Eats 外送撥款入帳_隨意小吃_09/17~09/23外送款</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>14615</v>
+      </c>
+      <c r="O153" t="n">
+        <v>14615</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Uber Eats 外送撥款 (款項日: 09/17~09/23外送款)</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr"/>
+      <c r="AL153" t="inlineStr"/>
+      <c r="AM153" t="inlineStr"/>
+      <c r="AN153" t="inlineStr"/>
+      <c r="AO153" t="inlineStr"/>
+      <c r="AP153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Uber Eats 外送撥款入帳_隨意小吃_09/17~09/23外送款</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>1130-03</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>14615</v>
+      </c>
+      <c r="O154" t="n">
+        <v>14615</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="inlineStr"/>
+      <c r="AK154" t="inlineStr"/>
+      <c r="AL154" t="inlineStr"/>
+      <c r="AM154" t="inlineStr"/>
+      <c r="AN154" t="inlineStr"/>
+      <c r="AO154" t="inlineStr"/>
+      <c r="AP154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>14009</v>
+      </c>
+      <c r="O155" t="n">
+        <v>14009</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/03營業款)</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr"/>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr"/>
+      <c r="AJ155" t="inlineStr"/>
+      <c r="AK155" t="inlineStr"/>
+      <c r="AL155" t="inlineStr"/>
+      <c r="AM155" t="inlineStr"/>
+      <c r="AN155" t="inlineStr"/>
+      <c r="AO155" t="inlineStr"/>
+      <c r="AP155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>1</v>
+      </c>
+      <c r="N156" t="n">
+        <v>434</v>
+      </c>
+      <c r="O156" t="n">
+        <v>434</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>LINE Pay 交易手續費</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr"/>
+      <c r="AJ156" t="inlineStr"/>
+      <c r="AK156" t="inlineStr"/>
+      <c r="AL156" t="inlineStr"/>
+      <c r="AM156" t="inlineStr"/>
+      <c r="AN156" t="inlineStr"/>
+      <c r="AO156" t="inlineStr"/>
+      <c r="AP156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>3</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>22</v>
+      </c>
+      <c r="O157" t="n">
+        <v>22</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>LINE Pay 手續費進項稅額</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="inlineStr"/>
+      <c r="AK157" t="inlineStr"/>
+      <c r="AL157" t="inlineStr"/>
+      <c r="AM157" t="inlineStr"/>
+      <c r="AN157" t="inlineStr"/>
+      <c r="AO157" t="inlineStr"/>
+      <c r="AP157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/03營業款</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>4</v>
+      </c>
+      <c r="F158" t="n">
+        <v>2</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>1130-02</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>14465</v>
+      </c>
+      <c r="O158" t="n">
+        <v>14465</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>沖銷 約10/03營業款 LINE Pay 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="inlineStr"/>
+      <c r="AK158" t="inlineStr"/>
+      <c r="AL158" t="inlineStr"/>
+      <c r="AM158" t="inlineStr"/>
+      <c r="AN158" t="inlineStr"/>
+      <c r="AO158" t="inlineStr"/>
+      <c r="AP158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/05電支款</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>29827</v>
+      </c>
+      <c r="O159" t="n">
+        <v>29827</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/05電支款)</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr"/>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="inlineStr"/>
+      <c r="AK159" t="inlineStr"/>
+      <c r="AL159" t="inlineStr"/>
+      <c r="AM159" t="inlineStr"/>
+      <c r="AN159" t="inlineStr"/>
+      <c r="AO159" t="inlineStr"/>
+      <c r="AP159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/05電支款</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1130-02</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
+        <v>29827</v>
+      </c>
+      <c r="O160" t="n">
+        <v>29827</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="inlineStr"/>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr"/>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="inlineStr"/>
+      <c r="AO160" t="inlineStr"/>
+      <c r="AP160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Foodpanda 外送撥款入帳_隨意小吃_上月下半月(16~30日)外送款</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>7255</v>
+      </c>
+      <c r="O161" t="n">
+        <v>7255</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Foodpanda 外送撥款 (款項日: 上月下半月(16~30日)外送款)</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="inlineStr"/>
+      <c r="AK161" t="inlineStr"/>
+      <c r="AL161" t="inlineStr"/>
+      <c r="AM161" t="inlineStr"/>
+      <c r="AN161" t="inlineStr"/>
+      <c r="AO161" t="inlineStr"/>
+      <c r="AP161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Foodpanda 外送撥款入帳_隨意小吃_上月下半月(16~30日)外送款</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>1130-04</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="n">
+        <v>7255</v>
+      </c>
+      <c r="O162" t="n">
+        <v>7255</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>沖銷 上月下半月(16~30日)外送款 Foodpanda 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="inlineStr"/>
+      <c r="AK162" t="inlineStr"/>
+      <c r="AL162" t="inlineStr"/>
+      <c r="AM162" t="inlineStr"/>
+      <c r="AN162" t="inlineStr"/>
+      <c r="AO162" t="inlineStr"/>
+      <c r="AP162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>3</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>18024</v>
+      </c>
+      <c r="O163" t="n">
+        <v>18024</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>LINE Pay 撥款入帳淨額 (款項日: 約10/10營業款)</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="inlineStr"/>
+      <c r="AK163" t="inlineStr"/>
+      <c r="AL163" t="inlineStr"/>
+      <c r="AM163" t="inlineStr"/>
+      <c r="AN163" t="inlineStr"/>
+      <c r="AO163" t="inlineStr"/>
+      <c r="AP163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>558</v>
+      </c>
+      <c r="O164" t="n">
+        <v>558</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>LINE Pay 交易手續費</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="inlineStr"/>
+      <c r="AK164" t="inlineStr"/>
+      <c r="AL164" t="inlineStr"/>
+      <c r="AM164" t="inlineStr"/>
+      <c r="AN164" t="inlineStr"/>
+      <c r="AO164" t="inlineStr"/>
+      <c r="AP164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>3</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>28</v>
+      </c>
+      <c r="O165" t="n">
+        <v>28</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>LINE Pay 手續費進項稅額</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="inlineStr"/>
+      <c r="AK165" t="inlineStr"/>
+      <c r="AL165" t="inlineStr"/>
+      <c r="AM165" t="inlineStr"/>
+      <c r="AN165" t="inlineStr"/>
+      <c r="AO165" t="inlineStr"/>
+      <c r="AP165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>連加網路(LINE Pay)撥款入帳_隨意小吃_約10/10營業款</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>4</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>1130-02</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>18610</v>
+      </c>
+      <c r="O166" t="n">
+        <v>18610</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>沖銷 約10/10營業款 LINE Pay 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr"/>
+      <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
+      <c r="AN166" t="inlineStr"/>
+      <c r="AO166" t="inlineStr"/>
+      <c r="AP166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/12電支款</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>32130</v>
+      </c>
+      <c r="O167" t="n">
+        <v>32130</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>LINE Pay 電子支付提領 (款項日: 約10/12電支款)</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="inlineStr"/>
+      <c r="AK167" t="inlineStr"/>
+      <c r="AL167" t="inlineStr"/>
+      <c r="AM167" t="inlineStr"/>
+      <c r="AN167" t="inlineStr"/>
+      <c r="AO167" t="inlineStr"/>
+      <c r="AP167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>連加電子支付(LINE Pay)提領入帳_隨意小吃_約10/12電支款</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1130-02</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>32130</v>
+      </c>
+      <c r="O168" t="n">
+        <v>32130</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
+      <c r="AJ168" t="inlineStr"/>
+      <c r="AK168" t="inlineStr"/>
+      <c r="AL168" t="inlineStr"/>
+      <c r="AM168" t="inlineStr"/>
+      <c r="AN168" t="inlineStr"/>
+      <c r="AO168" t="inlineStr"/>
+      <c r="AP168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>3</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Uber Eats 外送撥款入帳_隨意小吃_10/01~10/07外送款</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>5301</v>
+      </c>
+      <c r="O169" t="n">
+        <v>5301</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Uber Eats 外送撥款 (款項日: 10/01~10/07外送款)</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
+      <c r="AJ169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr"/>
+      <c r="AL169" t="inlineStr"/>
+      <c r="AM169" t="inlineStr"/>
+      <c r="AN169" t="inlineStr"/>
+      <c r="AO169" t="inlineStr"/>
+      <c r="AP169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Uber Eats 外送撥款入帳_隨意小吃_10/01~10/07外送款</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>1130-03</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>5301</v>
+      </c>
+      <c r="O170" t="n">
+        <v>5301</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
+      <c r="AJ170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr"/>
+      <c r="AL170" t="inlineStr"/>
+      <c r="AM170" t="inlineStr"/>
+      <c r="AN170" t="inlineStr"/>
+      <c r="AO170" t="inlineStr"/>
+      <c r="AP170" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
